--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125972595</v>
       </c>
       <c r="B3" t="n">
-        <v>58507</v>
+        <v>58508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,6 +984,3324 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126189751</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>583556</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6968527</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126189754</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>658</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>583666</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6968555</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar på två lågor</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126189650</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>583578</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6968472</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126189740</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>583431</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6968474</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126189743</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>658</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>583500</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6968467</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126189645</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>583487</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6968485</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126189742</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>658</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>583436</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6968539</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126189647</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>583543</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6968437</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126189646</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>583506</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6968453</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126189667</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>583448</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6968420</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påtaglig förekomst på sälg</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126189641</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>583440</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6968514</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126189651</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>583601</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6968490</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126189597</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>583530</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6968575</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ett par som är uppenbart irriterade på min närvaro. Flyger mot mig</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126189741</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>658</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>583419</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6968497</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126189644</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>583453</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6968516</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126189593</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>583491</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6968482</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Häckande</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126189746</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91246</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>583545</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6968439</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126189753</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91197</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>583523</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6968631</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126189755</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>658</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>583677</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6968571</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar på en låga</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126189747</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>583562</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6968428</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126189749</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>658</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>583575</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6968512</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126189744</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>583534</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6968451</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126189668</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>583415</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6968512</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126189642</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>583442</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6968524</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126189595</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>583576</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6968512</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lockrop</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126189649</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>583551</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6968411</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126189748</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91197</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>583604</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6968490</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126189750</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91686</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>583581</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6968518</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125966235</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125972595</v>
       </c>
       <c r="B3" t="n">
-        <v>58508</v>
+        <v>58509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125966107</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126189751</v>
       </c>
       <c r="B5" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>126189754</v>
       </c>
       <c r="B6" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,42 +1223,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126189650</v>
+        <v>126189740</v>
       </c>
       <c r="B7" t="n">
-        <v>98360</v>
+        <v>91234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583578</v>
+        <v>583431</v>
       </c>
       <c r="R7" t="n">
-        <v>6968472</v>
+        <v>6968474</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126189740</v>
+        <v>126189743</v>
       </c>
       <c r="B8" t="n">
-        <v>91232</v>
+        <v>91530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583431</v>
+        <v>583500</v>
       </c>
       <c r="R8" t="n">
-        <v>6968474</v>
+        <v>6968467</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,42 +1455,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126189743</v>
+        <v>126189650</v>
       </c>
       <c r="B9" t="n">
-        <v>91528</v>
+        <v>98362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583500</v>
+        <v>583578</v>
       </c>
       <c r="R9" t="n">
-        <v>6968467</v>
+        <v>6968472</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,7 +1574,7 @@
         <v>126189645</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>126189742</v>
       </c>
       <c r="B11" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>126189647</v>
       </c>
       <c r="B12" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>126189646</v>
       </c>
       <c r="B13" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>126189667</v>
       </c>
       <c r="B14" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>126189641</v>
       </c>
       <c r="B15" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>126189651</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126189597</v>
       </c>
       <c r="B17" t="n">
-        <v>58079</v>
+        <v>58080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>126189741</v>
       </c>
       <c r="B18" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>126189644</v>
       </c>
       <c r="B19" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>126189593</v>
       </c>
       <c r="B20" t="n">
-        <v>58079</v>
+        <v>58080</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>126189746</v>
       </c>
       <c r="B21" t="n">
-        <v>91246</v>
+        <v>91248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,32 +3003,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126189753</v>
+        <v>126189747</v>
       </c>
       <c r="B22" t="n">
-        <v>91197</v>
+        <v>91234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583523</v>
+        <v>583562</v>
       </c>
       <c r="R22" t="n">
-        <v>6968631</v>
+        <v>6968428</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3119,37 +3119,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126189755</v>
+        <v>126189753</v>
       </c>
       <c r="B23" t="n">
-        <v>91528</v>
+        <v>91199</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583677</v>
+        <v>583523</v>
       </c>
       <c r="R23" t="n">
-        <v>6968571</v>
+        <v>6968631</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3208,12 +3208,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar på en låga</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3240,10 +3235,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126189747</v>
+        <v>126189755</v>
       </c>
       <c r="B24" t="n">
-        <v>91232</v>
+        <v>91530</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,26 +3246,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3284,10 +3279,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583562</v>
+        <v>583677</v>
       </c>
       <c r="R24" t="n">
-        <v>6968428</v>
+        <v>6968571</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3319,7 +3314,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3329,7 +3324,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar på en låga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3359,7 +3359,7 @@
         <v>126189749</v>
       </c>
       <c r="B25" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189744</v>
+        <v>126189668</v>
       </c>
       <c r="B26" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,31 +3483,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583534</v>
+        <v>583415</v>
       </c>
       <c r="R26" t="n">
-        <v>6968451</v>
+        <v>6968512</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,7 +3561,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3588,10 +3593,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126189668</v>
+        <v>126189744</v>
       </c>
       <c r="B27" t="n">
-        <v>80075</v>
+        <v>91234</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,31 +3604,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3632,10 +3637,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583415</v>
+        <v>583534</v>
       </c>
       <c r="R27" t="n">
-        <v>6968512</v>
+        <v>6968451</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3667,7 +3672,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3677,12 +3682,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3709,42 +3709,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126189642</v>
+        <v>126189595</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>57649</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3753,10 +3763,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583442</v>
+        <v>583576</v>
       </c>
       <c r="R28" t="n">
-        <v>6968524</v>
+        <v>6968512</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3788,7 +3798,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3798,7 +3808,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Lockrop</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3825,52 +3840,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126189595</v>
+        <v>126189642</v>
       </c>
       <c r="B29" t="n">
-        <v>57648</v>
+        <v>98341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3879,10 +3884,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583576</v>
+        <v>583442</v>
       </c>
       <c r="R29" t="n">
-        <v>6968512</v>
+        <v>6968524</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3914,7 +3919,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3924,12 +3929,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lockrop</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3956,42 +3956,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126189649</v>
+        <v>126189748</v>
       </c>
       <c r="B30" t="n">
-        <v>98339</v>
+        <v>91199</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583551</v>
+        <v>583604</v>
       </c>
       <c r="R30" t="n">
-        <v>6968411</v>
+        <v>6968490</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4072,32 +4072,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126189748</v>
+        <v>126189750</v>
       </c>
       <c r="B31" t="n">
-        <v>91197</v>
+        <v>91688</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583604</v>
+        <v>583581</v>
       </c>
       <c r="R31" t="n">
-        <v>6968490</v>
+        <v>6968518</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4188,10 +4188,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126189750</v>
+        <v>126189649</v>
       </c>
       <c r="B32" t="n">
-        <v>91686</v>
+        <v>98341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4199,31 +4199,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583581</v>
+        <v>583551</v>
       </c>
       <c r="R32" t="n">
-        <v>6968518</v>
+        <v>6968411</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>126189751</v>
       </c>
       <c r="B5" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>126189754</v>
       </c>
       <c r="B6" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126189740</v>
       </c>
       <c r="B7" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>126189743</v>
       </c>
       <c r="B8" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>126189650</v>
       </c>
       <c r="B9" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,42 +1571,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126189645</v>
+        <v>126189742</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>91532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583487</v>
+        <v>583436</v>
       </c>
       <c r="R10" t="n">
-        <v>6968485</v>
+        <v>6968539</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,42 +1687,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189742</v>
+        <v>126189645</v>
       </c>
       <c r="B11" t="n">
-        <v>91530</v>
+        <v>98343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583436</v>
+        <v>583487</v>
       </c>
       <c r="R11" t="n">
-        <v>6968539</v>
+        <v>6968485</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,7 +1806,7 @@
         <v>126189647</v>
       </c>
       <c r="B12" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>126189646</v>
       </c>
       <c r="B13" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>126189641</v>
       </c>
       <c r="B15" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>126189651</v>
       </c>
       <c r="B16" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>126189741</v>
       </c>
       <c r="B18" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,42 +2640,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126189644</v>
+        <v>126189593</v>
       </c>
       <c r="B19" t="n">
-        <v>98341</v>
+        <v>58080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2684,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583453</v>
+        <v>583491</v>
       </c>
       <c r="R19" t="n">
-        <v>6968516</v>
+        <v>6968482</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2719,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,7 +2739,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Häckande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,52 +2771,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126189593</v>
+        <v>126189644</v>
       </c>
       <c r="B20" t="n">
-        <v>58080</v>
+        <v>98343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2810,10 +2815,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583491</v>
+        <v>583453</v>
       </c>
       <c r="R20" t="n">
-        <v>6968482</v>
+        <v>6968516</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2845,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,12 +2860,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Häckande</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2890,7 +2890,7 @@
         <v>126189746</v>
       </c>
       <c r="B21" t="n">
-        <v>91248</v>
+        <v>91250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>126189747</v>
       </c>
       <c r="B22" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>126189753</v>
       </c>
       <c r="B23" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>126189755</v>
       </c>
       <c r="B24" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>126189749</v>
       </c>
       <c r="B25" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>126189744</v>
       </c>
       <c r="B27" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3709,52 +3709,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126189595</v>
+        <v>126189642</v>
       </c>
       <c r="B28" t="n">
-        <v>57649</v>
+        <v>98343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3763,10 +3753,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583576</v>
+        <v>583442</v>
       </c>
       <c r="R28" t="n">
-        <v>6968512</v>
+        <v>6968524</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3798,7 +3788,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3808,12 +3798,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Lockrop</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3840,42 +3825,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126189642</v>
+        <v>126189595</v>
       </c>
       <c r="B29" t="n">
-        <v>98341</v>
+        <v>57649</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583442</v>
+        <v>583576</v>
       </c>
       <c r="R29" t="n">
-        <v>6968524</v>
+        <v>6968512</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3919,7 +3914,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3929,7 +3924,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lockrop</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3956,42 +3956,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126189748</v>
+        <v>126189649</v>
       </c>
       <c r="B30" t="n">
-        <v>91199</v>
+        <v>98343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583604</v>
+        <v>583551</v>
       </c>
       <c r="R30" t="n">
-        <v>6968490</v>
+        <v>6968411</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4075,7 +4075,7 @@
         <v>126189750</v>
       </c>
       <c r="B31" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4188,42 +4188,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126189649</v>
+        <v>126189748</v>
       </c>
       <c r="B32" t="n">
-        <v>98341</v>
+        <v>91201</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583551</v>
+        <v>583604</v>
       </c>
       <c r="R32" t="n">
-        <v>6968411</v>
+        <v>6968490</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126189740</v>
+        <v>126189743</v>
       </c>
       <c r="B7" t="n">
-        <v>91236</v>
+        <v>91532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583431</v>
+        <v>583500</v>
       </c>
       <c r="R7" t="n">
-        <v>6968474</v>
+        <v>6968467</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126189743</v>
+        <v>126189740</v>
       </c>
       <c r="B8" t="n">
-        <v>91532</v>
+        <v>91236</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583500</v>
+        <v>583431</v>
       </c>
       <c r="R8" t="n">
-        <v>6968467</v>
+        <v>6968474</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3956,10 +3956,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126189649</v>
+        <v>126189750</v>
       </c>
       <c r="B30" t="n">
-        <v>98343</v>
+        <v>91690</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,31 +3967,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583551</v>
+        <v>583581</v>
       </c>
       <c r="R30" t="n">
-        <v>6968411</v>
+        <v>6968518</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4072,32 +4072,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126189750</v>
+        <v>126189748</v>
       </c>
       <c r="B31" t="n">
-        <v>91690</v>
+        <v>91201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583581</v>
+        <v>583604</v>
       </c>
       <c r="R31" t="n">
-        <v>6968518</v>
+        <v>6968490</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4188,42 +4188,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126189748</v>
+        <v>126189649</v>
       </c>
       <c r="B32" t="n">
-        <v>91201</v>
+        <v>98343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583604</v>
+        <v>583551</v>
       </c>
       <c r="R32" t="n">
-        <v>6968490</v>
+        <v>6968411</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>126189751</v>
       </c>
       <c r="B5" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>126189754</v>
       </c>
       <c r="B6" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126189743</v>
+        <v>126189740</v>
       </c>
       <c r="B7" t="n">
-        <v>91532</v>
+        <v>91238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583500</v>
+        <v>583431</v>
       </c>
       <c r="R7" t="n">
-        <v>6968467</v>
+        <v>6968474</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126189740</v>
+        <v>126189743</v>
       </c>
       <c r="B8" t="n">
-        <v>91236</v>
+        <v>91534</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583431</v>
+        <v>583500</v>
       </c>
       <c r="R8" t="n">
-        <v>6968474</v>
+        <v>6968467</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,7 +1458,7 @@
         <v>126189650</v>
       </c>
       <c r="B9" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>126189742</v>
       </c>
       <c r="B10" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>126189645</v>
       </c>
       <c r="B11" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,37 +1803,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126189647</v>
+        <v>126189646</v>
       </c>
       <c r="B12" t="n">
-        <v>98242</v>
+        <v>98345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583543</v>
+        <v>583506</v>
       </c>
       <c r="R12" t="n">
-        <v>6968437</v>
+        <v>6968453</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,37 +1919,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126189646</v>
+        <v>126189647</v>
       </c>
       <c r="B13" t="n">
-        <v>98343</v>
+        <v>98244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583506</v>
+        <v>583543</v>
       </c>
       <c r="R13" t="n">
-        <v>6968453</v>
+        <v>6968437</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2159,7 +2159,7 @@
         <v>126189641</v>
       </c>
       <c r="B15" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>126189651</v>
       </c>
       <c r="B16" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>126189741</v>
       </c>
       <c r="B18" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>126189644</v>
       </c>
       <c r="B20" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>126189746</v>
       </c>
       <c r="B21" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,32 +3003,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126189747</v>
+        <v>126189753</v>
       </c>
       <c r="B22" t="n">
-        <v>91236</v>
+        <v>91203</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583562</v>
+        <v>583523</v>
       </c>
       <c r="R22" t="n">
-        <v>6968428</v>
+        <v>6968631</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3119,32 +3119,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126189753</v>
+        <v>126189747</v>
       </c>
       <c r="B23" t="n">
-        <v>91201</v>
+        <v>91238</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583523</v>
+        <v>583562</v>
       </c>
       <c r="R23" t="n">
-        <v>6968631</v>
+        <v>6968428</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,7 +3238,7 @@
         <v>126189755</v>
       </c>
       <c r="B24" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>126189749</v>
       </c>
       <c r="B25" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>126189744</v>
       </c>
       <c r="B27" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3709,42 +3709,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126189642</v>
+        <v>126189595</v>
       </c>
       <c r="B28" t="n">
-        <v>98343</v>
+        <v>57649</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3753,10 +3763,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583442</v>
+        <v>583576</v>
       </c>
       <c r="R28" t="n">
-        <v>6968524</v>
+        <v>6968512</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3788,7 +3798,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3798,7 +3808,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Lockrop</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3825,52 +3840,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126189595</v>
+        <v>126189642</v>
       </c>
       <c r="B29" t="n">
-        <v>57649</v>
+        <v>98345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3879,10 +3884,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583576</v>
+        <v>583442</v>
       </c>
       <c r="R29" t="n">
-        <v>6968512</v>
+        <v>6968524</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3914,7 +3919,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3924,12 +3929,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lockrop</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3959,7 +3959,7 @@
         <v>126189750</v>
       </c>
       <c r="B30" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,42 +4072,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126189748</v>
+        <v>126189649</v>
       </c>
       <c r="B31" t="n">
-        <v>91201</v>
+        <v>98345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583604</v>
+        <v>583551</v>
       </c>
       <c r="R31" t="n">
-        <v>6968490</v>
+        <v>6968411</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4188,42 +4188,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126189649</v>
+        <v>126189748</v>
       </c>
       <c r="B32" t="n">
-        <v>98343</v>
+        <v>91203</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583551</v>
+        <v>583604</v>
       </c>
       <c r="R32" t="n">
-        <v>6968411</v>
+        <v>6968490</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -1803,37 +1803,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126189646</v>
+        <v>126189647</v>
       </c>
       <c r="B12" t="n">
-        <v>98345</v>
+        <v>98244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583506</v>
+        <v>583543</v>
       </c>
       <c r="R12" t="n">
-        <v>6968453</v>
+        <v>6968437</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,37 +1919,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126189647</v>
+        <v>126189646</v>
       </c>
       <c r="B13" t="n">
-        <v>98244</v>
+        <v>98345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583543</v>
+        <v>583506</v>
       </c>
       <c r="R13" t="n">
-        <v>6968437</v>
+        <v>6968453</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3472,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189668</v>
+        <v>126189744</v>
       </c>
       <c r="B26" t="n">
-        <v>80076</v>
+        <v>91238</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,31 +3483,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583415</v>
+        <v>583534</v>
       </c>
       <c r="R26" t="n">
-        <v>6968512</v>
+        <v>6968451</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,12 +3561,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3593,10 +3588,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126189744</v>
+        <v>126189668</v>
       </c>
       <c r="B27" t="n">
-        <v>91238</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3604,31 +3599,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3637,10 +3632,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583534</v>
+        <v>583415</v>
       </c>
       <c r="R27" t="n">
-        <v>6968451</v>
+        <v>6968512</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3672,7 +3667,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3682,7 +3677,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125966235</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125972595</v>
       </c>
       <c r="B3" t="n">
-        <v>58509</v>
+        <v>58513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125966107</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126189751</v>
       </c>
       <c r="B5" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>126189754</v>
       </c>
       <c r="B6" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,42 +1223,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126189740</v>
+        <v>126189650</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>98370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583431</v>
+        <v>583578</v>
       </c>
       <c r="R7" t="n">
-        <v>6968474</v>
+        <v>6968472</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126189743</v>
+        <v>126189740</v>
       </c>
       <c r="B8" t="n">
-        <v>91534</v>
+        <v>91242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583500</v>
+        <v>583431</v>
       </c>
       <c r="R8" t="n">
-        <v>6968467</v>
+        <v>6968474</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,42 +1455,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126189650</v>
+        <v>126189743</v>
       </c>
       <c r="B9" t="n">
-        <v>98366</v>
+        <v>91538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583578</v>
+        <v>583500</v>
       </c>
       <c r="R9" t="n">
-        <v>6968472</v>
+        <v>6968467</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,7 +1574,7 @@
         <v>126189742</v>
       </c>
       <c r="B10" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>126189645</v>
       </c>
       <c r="B11" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>126189647</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>98248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>126189646</v>
       </c>
       <c r="B13" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>126189667</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>126189641</v>
       </c>
       <c r="B15" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>126189651</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126189597</v>
       </c>
       <c r="B17" t="n">
-        <v>58080</v>
+        <v>58084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>126189741</v>
       </c>
       <c r="B18" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>126189593</v>
       </c>
       <c r="B19" t="n">
-        <v>58080</v>
+        <v>58084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>126189644</v>
       </c>
       <c r="B20" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>126189746</v>
       </c>
       <c r="B21" t="n">
-        <v>91252</v>
+        <v>91256</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>126189753</v>
       </c>
       <c r="B22" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>126189747</v>
       </c>
       <c r="B23" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>126189755</v>
       </c>
       <c r="B24" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>126189749</v>
       </c>
       <c r="B25" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>126189744</v>
       </c>
       <c r="B26" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>126189668</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>126189595</v>
       </c>
       <c r="B28" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>126189642</v>
       </c>
       <c r="B29" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3956,10 +3956,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126189750</v>
+        <v>126189649</v>
       </c>
       <c r="B30" t="n">
-        <v>91692</v>
+        <v>98349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,31 +3967,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583581</v>
+        <v>583551</v>
       </c>
       <c r="R30" t="n">
-        <v>6968518</v>
+        <v>6968411</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4072,10 +4072,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126189649</v>
+        <v>126189750</v>
       </c>
       <c r="B31" t="n">
-        <v>98345</v>
+        <v>91696</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4083,31 +4083,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583551</v>
+        <v>583581</v>
       </c>
       <c r="R31" t="n">
-        <v>6968411</v>
+        <v>6968518</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4191,7 +4191,7 @@
         <v>126189748</v>
       </c>
       <c r="B32" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -1223,42 +1223,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126189650</v>
+        <v>126189740</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>91242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583578</v>
+        <v>583431</v>
       </c>
       <c r="R7" t="n">
-        <v>6968472</v>
+        <v>6968474</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126189740</v>
+        <v>126189743</v>
       </c>
       <c r="B8" t="n">
-        <v>91242</v>
+        <v>91538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583431</v>
+        <v>583500</v>
       </c>
       <c r="R8" t="n">
-        <v>6968474</v>
+        <v>6968467</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,42 +1455,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126189743</v>
+        <v>126189650</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>98373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583500</v>
+        <v>583578</v>
       </c>
       <c r="R9" t="n">
-        <v>6968467</v>
+        <v>6968472</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1690,7 +1690,7 @@
         <v>126189645</v>
       </c>
       <c r="B11" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>126189647</v>
       </c>
       <c r="B12" t="n">
-        <v>98248</v>
+        <v>98251</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>126189646</v>
       </c>
       <c r="B13" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>126189641</v>
       </c>
       <c r="B15" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>126189651</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2640,52 +2640,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126189593</v>
+        <v>126189644</v>
       </c>
       <c r="B19" t="n">
-        <v>58084</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2694,10 +2684,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583491</v>
+        <v>583453</v>
       </c>
       <c r="R19" t="n">
-        <v>6968482</v>
+        <v>6968516</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2729,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,12 +2729,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Häckande</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2771,42 +2756,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126189644</v>
+        <v>126189593</v>
       </c>
       <c r="B20" t="n">
-        <v>98349</v>
+        <v>58084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2815,10 +2810,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583453</v>
+        <v>583491</v>
       </c>
       <c r="R20" t="n">
-        <v>6968516</v>
+        <v>6968482</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2850,7 +2845,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,7 +2855,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Häckande</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126189747</v>
+        <v>126189755</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>91538</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3130,26 +3130,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583562</v>
+        <v>583677</v>
       </c>
       <c r="R23" t="n">
-        <v>6968428</v>
+        <v>6968571</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3208,7 +3208,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar på en låga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3235,10 +3240,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126189755</v>
+        <v>126189747</v>
       </c>
       <c r="B24" t="n">
-        <v>91538</v>
+        <v>91242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3246,26 +3251,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3279,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583677</v>
+        <v>583562</v>
       </c>
       <c r="R24" t="n">
-        <v>6968571</v>
+        <v>6968428</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3314,7 +3319,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3324,12 +3329,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar på en låga</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3472,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189744</v>
+        <v>126189668</v>
       </c>
       <c r="B26" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,31 +3483,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583534</v>
+        <v>583415</v>
       </c>
       <c r="R26" t="n">
-        <v>6968451</v>
+        <v>6968512</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,7 +3561,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3588,10 +3593,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126189668</v>
+        <v>126189744</v>
       </c>
       <c r="B27" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,31 +3604,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3632,10 +3637,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583415</v>
+        <v>583534</v>
       </c>
       <c r="R27" t="n">
-        <v>6968512</v>
+        <v>6968451</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3667,7 +3672,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3677,12 +3682,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3843,7 +3843,7 @@
         <v>126189642</v>
       </c>
       <c r="B29" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3956,42 +3956,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126189649</v>
+        <v>126189748</v>
       </c>
       <c r="B30" t="n">
-        <v>98349</v>
+        <v>91207</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583551</v>
+        <v>583604</v>
       </c>
       <c r="R30" t="n">
-        <v>6968411</v>
+        <v>6968490</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4188,42 +4188,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126189748</v>
+        <v>126189649</v>
       </c>
       <c r="B32" t="n">
-        <v>91207</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583604</v>
+        <v>583551</v>
       </c>
       <c r="R32" t="n">
-        <v>6968490</v>
+        <v>6968411</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -1571,42 +1571,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126189742</v>
+        <v>126189645</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583436</v>
+        <v>583487</v>
       </c>
       <c r="R10" t="n">
-        <v>6968539</v>
+        <v>6968485</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,42 +1687,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189645</v>
+        <v>126189742</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>91538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583487</v>
+        <v>583436</v>
       </c>
       <c r="R11" t="n">
-        <v>6968485</v>
+        <v>6968539</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3003,37 +3003,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126189753</v>
+        <v>126189755</v>
       </c>
       <c r="B22" t="n">
-        <v>91207</v>
+        <v>91538</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583523</v>
+        <v>583677</v>
       </c>
       <c r="R22" t="n">
-        <v>6968631</v>
+        <v>6968571</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3092,7 +3092,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar på en låga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3119,10 +3124,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126189755</v>
+        <v>126189747</v>
       </c>
       <c r="B23" t="n">
-        <v>91538</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3130,26 +3135,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3163,10 +3168,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583677</v>
+        <v>583562</v>
       </c>
       <c r="R23" t="n">
-        <v>6968571</v>
+        <v>6968428</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3198,7 +3203,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3208,12 +3213,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar på en låga</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3240,32 +3240,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126189747</v>
+        <v>126189753</v>
       </c>
       <c r="B24" t="n">
-        <v>91242</v>
+        <v>91207</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583562</v>
+        <v>583523</v>
       </c>
       <c r="R24" t="n">
-        <v>6968428</v>
+        <v>6968631</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3956,32 +3956,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126189748</v>
+        <v>126189750</v>
       </c>
       <c r="B30" t="n">
-        <v>91207</v>
+        <v>91696</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583604</v>
+        <v>583581</v>
       </c>
       <c r="R30" t="n">
-        <v>6968490</v>
+        <v>6968518</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4072,10 +4072,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126189750</v>
+        <v>126189649</v>
       </c>
       <c r="B31" t="n">
-        <v>91696</v>
+        <v>98352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4083,31 +4083,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583581</v>
+        <v>583551</v>
       </c>
       <c r="R31" t="n">
-        <v>6968518</v>
+        <v>6968411</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4188,42 +4188,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126189649</v>
+        <v>126189748</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>91207</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583551</v>
+        <v>583604</v>
       </c>
       <c r="R32" t="n">
-        <v>6968411</v>
+        <v>6968490</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126189740</v>
+        <v>126189743</v>
       </c>
       <c r="B7" t="n">
-        <v>91242</v>
+        <v>91538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583431</v>
+        <v>583500</v>
       </c>
       <c r="R7" t="n">
-        <v>6968474</v>
+        <v>6968467</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126189743</v>
+        <v>126189740</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>91242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583500</v>
+        <v>583431</v>
       </c>
       <c r="R8" t="n">
-        <v>6968467</v>
+        <v>6968474</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,42 +1571,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126189645</v>
+        <v>126189742</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>91538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583487</v>
+        <v>583436</v>
       </c>
       <c r="R10" t="n">
-        <v>6968485</v>
+        <v>6968539</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,42 +1687,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189742</v>
+        <v>126189645</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583436</v>
+        <v>583487</v>
       </c>
       <c r="R11" t="n">
-        <v>6968539</v>
+        <v>6968485</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2640,42 +2640,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126189644</v>
+        <v>126189593</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>58084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2684,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583453</v>
+        <v>583491</v>
       </c>
       <c r="R19" t="n">
-        <v>6968516</v>
+        <v>6968482</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2719,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,7 +2739,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Häckande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,52 +2771,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126189593</v>
+        <v>126189644</v>
       </c>
       <c r="B20" t="n">
-        <v>58084</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2810,10 +2815,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583491</v>
+        <v>583453</v>
       </c>
       <c r="R20" t="n">
-        <v>6968482</v>
+        <v>6968516</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2845,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,12 +2860,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Häckande</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3003,37 +3003,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126189755</v>
+        <v>126189753</v>
       </c>
       <c r="B22" t="n">
-        <v>91538</v>
+        <v>91207</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583677</v>
+        <v>583523</v>
       </c>
       <c r="R22" t="n">
-        <v>6968571</v>
+        <v>6968631</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3092,12 +3092,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar på en låga</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3124,10 +3119,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126189747</v>
+        <v>126189755</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>91538</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3135,26 +3130,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3168,10 +3163,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583562</v>
+        <v>583677</v>
       </c>
       <c r="R23" t="n">
-        <v>6968428</v>
+        <v>6968571</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3203,7 +3198,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3213,7 +3208,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar på en låga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3240,32 +3240,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126189753</v>
+        <v>126189747</v>
       </c>
       <c r="B24" t="n">
-        <v>91207</v>
+        <v>91242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583523</v>
+        <v>583562</v>
       </c>
       <c r="R24" t="n">
-        <v>6968631</v>
+        <v>6968428</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3709,52 +3709,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126189595</v>
+        <v>126189642</v>
       </c>
       <c r="B28" t="n">
-        <v>57653</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3763,10 +3753,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583576</v>
+        <v>583442</v>
       </c>
       <c r="R28" t="n">
-        <v>6968512</v>
+        <v>6968524</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3798,7 +3788,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3808,12 +3798,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Lockrop</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3840,42 +3825,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126189642</v>
+        <v>126189595</v>
       </c>
       <c r="B29" t="n">
-        <v>98352</v>
+        <v>57653</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583442</v>
+        <v>583576</v>
       </c>
       <c r="R29" t="n">
-        <v>6968524</v>
+        <v>6968512</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3919,7 +3914,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3929,7 +3924,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lockrop</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4072,42 +4072,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126189649</v>
+        <v>126189748</v>
       </c>
       <c r="B31" t="n">
-        <v>98352</v>
+        <v>91207</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583551</v>
+        <v>583604</v>
       </c>
       <c r="R31" t="n">
-        <v>6968411</v>
+        <v>6968490</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4188,42 +4188,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126189748</v>
+        <v>126189649</v>
       </c>
       <c r="B32" t="n">
-        <v>91207</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583604</v>
+        <v>583551</v>
       </c>
       <c r="R32" t="n">
-        <v>6968490</v>
+        <v>6968411</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -1223,42 +1223,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126189743</v>
+        <v>126189650</v>
       </c>
       <c r="B7" t="n">
-        <v>91538</v>
+        <v>98373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583500</v>
+        <v>583578</v>
       </c>
       <c r="R7" t="n">
-        <v>6968467</v>
+        <v>6968472</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126189740</v>
+        <v>126189743</v>
       </c>
       <c r="B8" t="n">
-        <v>91242</v>
+        <v>91538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583431</v>
+        <v>583500</v>
       </c>
       <c r="R8" t="n">
-        <v>6968474</v>
+        <v>6968467</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,42 +1455,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126189650</v>
+        <v>126189740</v>
       </c>
       <c r="B9" t="n">
-        <v>98373</v>
+        <v>91242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583578</v>
+        <v>583431</v>
       </c>
       <c r="R9" t="n">
-        <v>6968472</v>
+        <v>6968474</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,42 +1571,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126189742</v>
+        <v>126189645</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583436</v>
+        <v>583487</v>
       </c>
       <c r="R10" t="n">
-        <v>6968539</v>
+        <v>6968485</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,42 +1687,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189645</v>
+        <v>126189742</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>91538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583487</v>
+        <v>583436</v>
       </c>
       <c r="R11" t="n">
-        <v>6968485</v>
+        <v>6968539</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3472,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189668</v>
+        <v>126189744</v>
       </c>
       <c r="B26" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,31 +3483,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583415</v>
+        <v>583534</v>
       </c>
       <c r="R26" t="n">
-        <v>6968512</v>
+        <v>6968451</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,12 +3561,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3593,10 +3588,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126189744</v>
+        <v>126189668</v>
       </c>
       <c r="B27" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3604,31 +3599,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3637,10 +3632,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583534</v>
+        <v>583415</v>
       </c>
       <c r="R27" t="n">
-        <v>6968451</v>
+        <v>6968512</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3672,7 +3667,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3682,7 +3677,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3956,32 +3956,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126189750</v>
+        <v>126189748</v>
       </c>
       <c r="B30" t="n">
-        <v>91696</v>
+        <v>91207</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583581</v>
+        <v>583604</v>
       </c>
       <c r="R30" t="n">
-        <v>6968518</v>
+        <v>6968490</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4072,32 +4072,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126189748</v>
+        <v>126189750</v>
       </c>
       <c r="B31" t="n">
-        <v>91207</v>
+        <v>91696</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583604</v>
+        <v>583581</v>
       </c>
       <c r="R31" t="n">
-        <v>6968490</v>
+        <v>6968518</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125966235</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125972595</v>
       </c>
       <c r="B3" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125966107</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126189751</v>
       </c>
       <c r="B5" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>126189754</v>
       </c>
       <c r="B6" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,42 +1223,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126189650</v>
+        <v>126189743</v>
       </c>
       <c r="B7" t="n">
-        <v>98373</v>
+        <v>91541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583578</v>
+        <v>583500</v>
       </c>
       <c r="R7" t="n">
-        <v>6968472</v>
+        <v>6968467</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126189743</v>
+        <v>126189740</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>91245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583500</v>
+        <v>583431</v>
       </c>
       <c r="R8" t="n">
-        <v>6968467</v>
+        <v>6968474</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,42 +1455,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126189740</v>
+        <v>126189650</v>
       </c>
       <c r="B9" t="n">
-        <v>91242</v>
+        <v>98382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583431</v>
+        <v>583578</v>
       </c>
       <c r="R9" t="n">
-        <v>6968474</v>
+        <v>6968472</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,42 +1571,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126189645</v>
+        <v>126189742</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>91541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583487</v>
+        <v>583436</v>
       </c>
       <c r="R10" t="n">
-        <v>6968485</v>
+        <v>6968539</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,42 +1687,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189742</v>
+        <v>126189645</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>98361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583436</v>
+        <v>583487</v>
       </c>
       <c r="R11" t="n">
-        <v>6968539</v>
+        <v>6968485</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,7 +1806,7 @@
         <v>126189647</v>
       </c>
       <c r="B12" t="n">
-        <v>98251</v>
+        <v>98260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>126189646</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>126189667</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>126189641</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>126189651</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126189597</v>
       </c>
       <c r="B17" t="n">
-        <v>58084</v>
+        <v>58087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>126189741</v>
       </c>
       <c r="B18" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>126189593</v>
       </c>
       <c r="B19" t="n">
-        <v>58084</v>
+        <v>58087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>126189644</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>126189746</v>
       </c>
       <c r="B21" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,37 +3003,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126189753</v>
+        <v>126189755</v>
       </c>
       <c r="B22" t="n">
-        <v>91207</v>
+        <v>91541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583523</v>
+        <v>583677</v>
       </c>
       <c r="R22" t="n">
-        <v>6968631</v>
+        <v>6968571</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3092,7 +3092,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar på en låga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3119,10 +3124,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126189755</v>
+        <v>126189747</v>
       </c>
       <c r="B23" t="n">
-        <v>91538</v>
+        <v>91245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3130,26 +3135,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3163,10 +3168,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583677</v>
+        <v>583562</v>
       </c>
       <c r="R23" t="n">
-        <v>6968571</v>
+        <v>6968428</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3198,7 +3203,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3208,12 +3213,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar på en låga</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3240,32 +3240,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126189747</v>
+        <v>126189753</v>
       </c>
       <c r="B24" t="n">
-        <v>91242</v>
+        <v>91210</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583562</v>
+        <v>583523</v>
       </c>
       <c r="R24" t="n">
-        <v>6968428</v>
+        <v>6968631</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3359,7 +3359,7 @@
         <v>126189749</v>
       </c>
       <c r="B25" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189744</v>
+        <v>126189668</v>
       </c>
       <c r="B26" t="n">
-        <v>91242</v>
+        <v>80083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,31 +3483,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583534</v>
+        <v>583415</v>
       </c>
       <c r="R26" t="n">
-        <v>6968451</v>
+        <v>6968512</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,7 +3561,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3588,10 +3593,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126189668</v>
+        <v>126189744</v>
       </c>
       <c r="B27" t="n">
-        <v>80080</v>
+        <v>91245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,31 +3604,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3632,10 +3637,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583415</v>
+        <v>583534</v>
       </c>
       <c r="R27" t="n">
-        <v>6968512</v>
+        <v>6968451</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3667,7 +3672,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3677,12 +3682,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3709,42 +3709,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126189642</v>
+        <v>126189595</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>57654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3753,10 +3763,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583442</v>
+        <v>583576</v>
       </c>
       <c r="R28" t="n">
-        <v>6968524</v>
+        <v>6968512</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3788,7 +3798,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3798,7 +3808,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Lockrop</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3825,52 +3840,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126189595</v>
+        <v>126189642</v>
       </c>
       <c r="B29" t="n">
-        <v>57653</v>
+        <v>98361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3879,10 +3884,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583576</v>
+        <v>583442</v>
       </c>
       <c r="R29" t="n">
-        <v>6968512</v>
+        <v>6968524</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3914,7 +3919,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3924,12 +3929,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lockrop</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3956,32 +3956,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126189748</v>
+        <v>126189750</v>
       </c>
       <c r="B30" t="n">
-        <v>91207</v>
+        <v>91699</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583604</v>
+        <v>583581</v>
       </c>
       <c r="R30" t="n">
-        <v>6968490</v>
+        <v>6968518</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4072,32 +4072,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126189750</v>
+        <v>126189748</v>
       </c>
       <c r="B31" t="n">
-        <v>91696</v>
+        <v>91210</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583581</v>
+        <v>583604</v>
       </c>
       <c r="R31" t="n">
-        <v>6968518</v>
+        <v>6968490</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4191,7 +4191,7 @@
         <v>126189649</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -3956,10 +3956,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126189750</v>
+        <v>126189649</v>
       </c>
       <c r="B30" t="n">
-        <v>91699</v>
+        <v>98361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,31 +3967,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583581</v>
+        <v>583551</v>
       </c>
       <c r="R30" t="n">
-        <v>6968518</v>
+        <v>6968411</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4072,32 +4072,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126189748</v>
+        <v>126189750</v>
       </c>
       <c r="B31" t="n">
-        <v>91210</v>
+        <v>91699</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583604</v>
+        <v>583581</v>
       </c>
       <c r="R31" t="n">
-        <v>6968490</v>
+        <v>6968518</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4188,42 +4188,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126189649</v>
+        <v>126189748</v>
       </c>
       <c r="B32" t="n">
-        <v>98361</v>
+        <v>91210</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583551</v>
+        <v>583604</v>
       </c>
       <c r="R32" t="n">
-        <v>6968411</v>
+        <v>6968490</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126189751</v>
+        <v>126189754</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>91541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,26 +997,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583556</v>
+        <v>583666</v>
       </c>
       <c r="R5" t="n">
-        <v>6968527</v>
+        <v>6968555</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1075,7 +1075,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar på två lågor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126189754</v>
+        <v>126189751</v>
       </c>
       <c r="B6" t="n">
-        <v>91541</v>
+        <v>91245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,26 +1118,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1146,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583666</v>
+        <v>583556</v>
       </c>
       <c r="R6" t="n">
-        <v>6968555</v>
+        <v>6968527</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1181,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,12 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>9 fruktkroppar på två lågor</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1339,42 +1339,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126189740</v>
+        <v>126189650</v>
       </c>
       <c r="B8" t="n">
-        <v>91245</v>
+        <v>98382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583431</v>
+        <v>583578</v>
       </c>
       <c r="R8" t="n">
-        <v>6968474</v>
+        <v>6968472</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,42 +1455,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126189650</v>
+        <v>126189740</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>91245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583578</v>
+        <v>583431</v>
       </c>
       <c r="R9" t="n">
-        <v>6968472</v>
+        <v>6968474</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3124,32 +3124,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126189747</v>
+        <v>126189753</v>
       </c>
       <c r="B23" t="n">
-        <v>91245</v>
+        <v>91210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583562</v>
+        <v>583523</v>
       </c>
       <c r="R23" t="n">
-        <v>6968428</v>
+        <v>6968631</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3240,32 +3240,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126189753</v>
+        <v>126189747</v>
       </c>
       <c r="B24" t="n">
-        <v>91210</v>
+        <v>91245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583523</v>
+        <v>583562</v>
       </c>
       <c r="R24" t="n">
-        <v>6968631</v>
+        <v>6968428</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3956,42 +3956,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126189649</v>
+        <v>126189748</v>
       </c>
       <c r="B30" t="n">
-        <v>98361</v>
+        <v>91210</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583551</v>
+        <v>583604</v>
       </c>
       <c r="R30" t="n">
-        <v>6968411</v>
+        <v>6968490</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4188,42 +4188,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126189748</v>
+        <v>126189649</v>
       </c>
       <c r="B32" t="n">
-        <v>91210</v>
+        <v>98361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583604</v>
+        <v>583551</v>
       </c>
       <c r="R32" t="n">
-        <v>6968490</v>
+        <v>6968411</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -3956,42 +3956,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126189748</v>
+        <v>126189649</v>
       </c>
       <c r="B30" t="n">
-        <v>91210</v>
+        <v>98361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583604</v>
+        <v>583551</v>
       </c>
       <c r="R30" t="n">
-        <v>6968490</v>
+        <v>6968411</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4072,32 +4072,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126189750</v>
+        <v>126189748</v>
       </c>
       <c r="B31" t="n">
-        <v>91699</v>
+        <v>91210</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583581</v>
+        <v>583604</v>
       </c>
       <c r="R31" t="n">
-        <v>6968518</v>
+        <v>6968490</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4188,10 +4188,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126189649</v>
+        <v>126189750</v>
       </c>
       <c r="B32" t="n">
-        <v>98361</v>
+        <v>91699</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4199,31 +4199,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583551</v>
+        <v>583581</v>
       </c>
       <c r="R32" t="n">
-        <v>6968411</v>
+        <v>6968518</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -3472,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189668</v>
+        <v>126189744</v>
       </c>
       <c r="B26" t="n">
-        <v>80083</v>
+        <v>91245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,31 +3483,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583415</v>
+        <v>583534</v>
       </c>
       <c r="R26" t="n">
-        <v>6968512</v>
+        <v>6968451</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,12 +3561,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3593,10 +3588,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126189744</v>
+        <v>126189668</v>
       </c>
       <c r="B27" t="n">
-        <v>91245</v>
+        <v>80083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3604,31 +3599,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3637,10 +3632,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583534</v>
+        <v>583415</v>
       </c>
       <c r="R27" t="n">
-        <v>6968451</v>
+        <v>6968512</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3672,7 +3667,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3682,7 +3677,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126189754</v>
+        <v>126189751</v>
       </c>
       <c r="B5" t="n">
-        <v>91541</v>
+        <v>91245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,26 +997,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583666</v>
+        <v>583556</v>
       </c>
       <c r="R5" t="n">
-        <v>6968555</v>
+        <v>6968527</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1075,12 +1075,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>9 fruktkroppar på två lågor</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126189751</v>
+        <v>126189754</v>
       </c>
       <c r="B6" t="n">
-        <v>91245</v>
+        <v>91541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,26 +1113,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1151,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583556</v>
+        <v>583666</v>
       </c>
       <c r="R6" t="n">
-        <v>6968527</v>
+        <v>6968555</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1191,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar på två lågor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3124,32 +3124,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126189753</v>
+        <v>126189747</v>
       </c>
       <c r="B23" t="n">
-        <v>91210</v>
+        <v>91245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583523</v>
+        <v>583562</v>
       </c>
       <c r="R23" t="n">
-        <v>6968631</v>
+        <v>6968428</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3240,32 +3240,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126189747</v>
+        <v>126189753</v>
       </c>
       <c r="B24" t="n">
-        <v>91245</v>
+        <v>91210</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583562</v>
+        <v>583523</v>
       </c>
       <c r="R24" t="n">
-        <v>6968428</v>
+        <v>6968631</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -3712,7 +3712,7 @@
         <v>126189595</v>
       </c>
       <c r="B28" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -3712,7 +3712,7 @@
         <v>126189595</v>
       </c>
       <c r="B28" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -3712,7 +3712,7 @@
         <v>126189595</v>
       </c>
       <c r="B28" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 60863-2023 artfynd.xlsx
+++ b/artfynd/A 60863-2023 artfynd.xlsx
@@ -3712,7 +3712,7 @@
         <v>126189595</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
